--- a/Projeto/Dashboard.xlsx
+++ b/Projeto/Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cassi\GitHub\projeto-excel\Projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAA11BF-668A-4140-A7A4-3E0F94F253E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FE4CD3-B131-4B0A-8BE8-61DF2065A3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="1681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="1682">
   <si>
     <t>Olist — Atrasos na Entrega e Satisfação do Cliente</t>
   </si>
@@ -5081,10 +5081,13 @@
     <t>prob_nota1</t>
   </si>
   <si>
-    <t>Top 10 sellers por atraso médio (mín. 5 atrasos)</t>
+    <t>Top 10 sellers por atraso médio (mín. 20 pedidos e 5 atrasos)</t>
   </si>
   <si>
     <t>Top 10 estados por atraso médio (mín. 10 atrasos)</t>
+  </si>
+  <si>
+    <t>Top 10 estados por taxa de atraso (mín. 100 pedidos)</t>
   </si>
 </sst>
 </file>
@@ -5528,7 +5531,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-42CF-44A7-98FC-F02DB11358DD}"/>
+              <c16:uniqueId val="{00000000-29E5-4251-95F9-D735E35EDEDE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5630,7 +5633,7 @@
                   <a:srgbClr val="404040"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Top 10 sellers por dias de atraso (mín. 5 atrasos)</a:t>
+              <a:t>Top 10 por dias de atraso (mín. 20 pedidos e 5 atrasos)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5784,7 +5787,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EDFE-43B9-9196-D0975B0F6901}"/>
+              <c16:uniqueId val="{00000000-A3A4-4080-995A-396988DB5687}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5928,7 +5931,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-91B3-49F7-86BB-E78B0AC4394D}"/>
+                <c16:uniqueId val="{00000001-B785-4604-A469-D9C2635AE4B7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5947,7 +5950,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-91B3-49F7-86BB-E78B0AC4394D}"/>
+                <c16:uniqueId val="{00000003-B785-4604-A469-D9C2635AE4B7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6030,7 +6033,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-91B3-49F7-86BB-E78B0AC4394D}"/>
+              <c16:uniqueId val="{00000004-B785-4604-A469-D9C2635AE4B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6176,7 +6179,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-4792-4A20-BF23-C1ED3BBA972C}"/>
+                <c16:uniqueId val="{00000001-F226-4803-BE9F-40359AA80C33}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6195,7 +6198,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-4792-4A20-BF23-C1ED3BBA972C}"/>
+                <c16:uniqueId val="{00000003-F226-4803-BE9F-40359AA80C33}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6278,7 +6281,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-4792-4A20-BF23-C1ED3BBA972C}"/>
+              <c16:uniqueId val="{00000004-F226-4803-BE9F-40359AA80C33}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6381,7 +6384,7 @@
                   <a:srgbClr val="404040"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Top 10 estados por taxa de atraso</a:t>
+              <a:t>Top 10 estados por taxa de atraso (mín. 100 pedidos)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -6445,7 +6448,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dados_Estados!$A$2:$A$11</c:f>
+              <c:f>Rankings!$G$3:$G$12</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -6464,26 +6467,26 @@
                   <c:v>CE</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>RR</c:v>
+                  <c:v>BA</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>BA</c:v>
+                  <c:v>RJ</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>RJ</c:v>
+                  <c:v>PA</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>PA</c:v>
+                  <c:v>ES</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>ES</c:v>
+                  <c:v>PB</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dados_Estados!$D$2:$D$11</c:f>
+              <c:f>Rankings!$H$3:$H$12</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -6503,19 +6506,19 @@
                   <c:v>0.1376</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.122</c:v>
+                  <c:v>0.1216</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1216</c:v>
+                  <c:v>0.1211</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1211</c:v>
+                  <c:v>0.11210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.11210000000000001</c:v>
+                  <c:v>0.10730000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.10730000000000001</c:v>
+                  <c:v>0.10440000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6535,7 +6538,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3287-4ECE-A010-B90B6079D084}"/>
+              <c16:uniqueId val="{00000000-1CF3-4803-8650-EF3ED7E4CADC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6791,7 +6794,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1AB7-4566-A40E-43056BDB018D}"/>
+              <c16:uniqueId val="{00000000-E2B7-4A3C-9671-BCFCB952BB83}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -24479,24 +24482,29 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1679</v>
       </c>
       <c r="D1" t="s">
         <v>1680</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -24509,8 +24517,14 @@
       <c r="E2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -24523,8 +24537,14 @@
       <c r="E3" s="3">
         <v>16.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.21410000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -24537,8 +24557,14 @@
       <c r="E4" s="3">
         <v>15.18</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.17430000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>740</v>
       </c>
@@ -24551,8 +24577,14 @@
       <c r="E5" s="3">
         <v>14.48</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>386</v>
       </c>
@@ -24565,8 +24597,14 @@
       <c r="E6" s="3">
         <v>13.52</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.13869999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -24579,8 +24617,14 @@
       <c r="E7" s="3">
         <v>13.35</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1376</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1006</v>
       </c>
@@ -24593,8 +24637,14 @@
       <c r="E8" s="3">
         <v>12.82</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G8" t="s">
+        <v>1653</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>864</v>
       </c>
@@ -24607,8 +24657,14 @@
       <c r="E9" s="3">
         <v>12.02</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>1654</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>532</v>
       </c>
@@ -24621,8 +24677,14 @@
       <c r="E10" s="3">
         <v>11.97</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.11210000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>496</v>
       </c>
@@ -24635,8 +24697,14 @@
       <c r="E11" s="3">
         <v>11.37</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.10730000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>108</v>
       </c>
@@ -24648,6 +24716,12 @@
       </c>
       <c r="E12" s="3">
         <v>11.3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1657</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.10440000000000001</v>
       </c>
     </row>
   </sheetData>
